--- a/data_room/hollis_voice_clean/02_financials/financial_model.xlsx
+++ b/data_room/hollis_voice_clean/02_financials/financial_model.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Hiring_Plan" sheetId="6" r:id="rId6"/>
     <sheet name="Cash_Runway" sheetId="7" r:id="rId7"/>
     <sheet name="Cash_Bridge" sheetId="8" r:id="rId8"/>
+    <sheet name="Market" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="ARR_TOTAL">ARR_Build!$E$15</definedName>
@@ -29,6 +30,9 @@
     <definedName name="HOSTING_USD_MONTH">Assumptions!$B$13</definedName>
     <definedName name="LICENCES_PCT">Assumptions!$B$12</definedName>
     <definedName name="LOAD_FACTOR">Assumptions!$B$8</definedName>
+    <definedName name="MARKET_ACV_USD">Market!$B$6</definedName>
+    <definedName name="MARKET_CLINICS">Market!$B$5</definedName>
+    <definedName name="MARKET_TAM_USD">Market!$B$7</definedName>
     <definedName name="NET_LOSS_BEFORE_2025_USD">Assumptions!$B$21</definedName>
     <definedName name="NRR_12M">Cohorts!$E$14</definedName>
     <definedName name="PAYROLL_NOW_USD_MONTH">Assumptions!$B$22</definedName>
@@ -49,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="290">
   <si>
     <t>Hollis Voice: financial model</t>
   </si>
@@ -81,6 +85,9 @@
     <t>Cash_Bridge: money raised, less losses since the company began, equals cash at the data date.</t>
   </si>
   <si>
+    <t>Market: the company's own market estimate, the one the deck's market slide uses.</t>
+  </si>
+  <si>
     <t>Definitions</t>
   </si>
   <si>
@@ -621,7 +628,7 @@
     <t>Implementation Specialist</t>
   </si>
   <si>
-    <t>Head of Sales</t>
+    <t>Director of Enterprise Sales</t>
   </si>
   <si>
     <t>Support Specialist</t>
@@ -669,9 +676,6 @@
     <t>Hires in this plan</t>
   </si>
   <si>
-    <t>Staff after these hires</t>
-  </si>
-  <si>
     <t>Cash and runway (USD)</t>
   </si>
   <si>
@@ -892,6 +896,33 @@
   </si>
   <si>
     <t>Rounding only: the loss before 2025 is stated in whole dollars.</t>
+  </si>
+  <si>
+    <t>Market size (USD)</t>
+  </si>
+  <si>
+    <t>These are the company's own estimates. No outside source is in the room.</t>
+  </si>
+  <si>
+    <t>US independent veterinary clinics (company estimate)</t>
+  </si>
+  <si>
+    <t>The same count as the deck's market slide.</t>
+  </si>
+  <si>
+    <t>Annual contract value per clinic (USD, company estimate)</t>
+  </si>
+  <si>
+    <t>A planning figure for what a clinic pays in a year.</t>
+  </si>
+  <si>
+    <t>Market size: clinics times annual contract value (USD)</t>
+  </si>
+  <si>
+    <t>For comparison: subscription ARR per paying clinic today (USD)</t>
+  </si>
+  <si>
+    <t>Subscription ARR in ARR_Build divided by the paying clinics counted there.</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -1358,13 +1389,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="2" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1383,9 +1414,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="3" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1405,227 +1441,227 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6">
         <v>1800000</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7">
         <v>0.035</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="6">
         <v>1.28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="6">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="6">
         <v>140000</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="7">
         <v>0.15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="7">
         <v>0.05</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6">
         <v>18891.29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="6">
         <v>60000</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6">
         <v>140000</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6">
         <v>9000000</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="6">
         <v>4</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="6">
         <v>171739</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="6">
         <v>2000000</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="6">
         <v>3400000</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="6">
         <v>501801</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="6">
         <f>STAFF_NOW*AVG_BASE_NOW*LOAD_FACTOR/12</f>
         <v>253866.66666666666</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1645,227 +1681,227 @@
   <sheetData>
     <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:35">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:35">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF4" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG4" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH4" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AI4" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:35">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:35">
       <c r="A6" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1904,10 +1940,10 @@
     </row>
     <row r="7" spans="1:35">
       <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
         <v>97</v>
-      </c>
-      <c r="B7" t="s">
-        <v>96</v>
       </c>
       <c r="C7" s="10">
         <v>2651</v>
@@ -1975,10 +2011,10 @@
     </row>
     <row r="8" spans="1:35">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
@@ -2046,10 +2082,10 @@
     </row>
     <row r="9" spans="1:35">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="10">
         <v>2500</v>
@@ -2153,10 +2189,10 @@
     </row>
     <row r="10" spans="1:35">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" s="10">
         <f>C7</f>
@@ -2281,10 +2317,10 @@
     </row>
     <row r="11" spans="1:35">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="10">
         <f>C10+C8+C9</f>
@@ -2421,7 +2457,7 @@
     </row>
     <row r="12" spans="1:35">
       <c r="A12" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2460,10 +2496,10 @@
     </row>
     <row r="13" spans="1:35">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="10">
         <v>435.7</v>
@@ -2567,10 +2603,10 @@
     </row>
     <row r="14" spans="1:35">
       <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
         <v>105</v>
-      </c>
-      <c r="B14" t="s">
-        <v>104</v>
       </c>
       <c r="C14" s="10">
         <v>148.48</v>
@@ -2674,10 +2710,10 @@
     </row>
     <row r="15" spans="1:35">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="10">
         <v>384.59</v>
@@ -2781,10 +2817,10 @@
     </row>
     <row r="16" spans="1:35">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -2888,10 +2924,10 @@
     </row>
     <row r="17" spans="1:35">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" s="10">
         <f>C13+C14+C15+C16</f>
@@ -3028,7 +3064,7 @@
     </row>
     <row r="18" spans="1:35">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="11">
         <f>C10-C17</f>
@@ -3165,7 +3201,7 @@
     </row>
     <row r="19" spans="1:35">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="12">
         <f>C18/C10</f>
@@ -3302,7 +3338,7 @@
     </row>
     <row r="20" spans="1:35">
       <c r="A20" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -3341,10 +3377,10 @@
     </row>
     <row r="21" spans="1:35">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C21" s="10">
         <v>31186.59</v>
@@ -3448,10 +3484,10 @@
     </row>
     <row r="22" spans="1:35">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="10">
         <v>14987.33</v>
@@ -3555,10 +3591,10 @@
     </row>
     <row r="23" spans="1:35">
       <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
         <v>116</v>
-      </c>
-      <c r="B23" t="s">
-        <v>115</v>
       </c>
       <c r="C23" s="10">
         <v>0</v>
@@ -3662,10 +3698,10 @@
     </row>
     <row r="24" spans="1:35">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" s="10">
         <v>15663.86</v>
@@ -3769,10 +3805,10 @@
     </row>
     <row r="25" spans="1:35">
       <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
         <v>119</v>
-      </c>
-      <c r="B25" t="s">
-        <v>118</v>
       </c>
       <c r="C25" s="10">
         <v>29694.61</v>
@@ -3876,7 +3912,7 @@
     </row>
     <row r="26" spans="1:35">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C26" s="11">
         <f>C21+C22+C23+C24+C25</f>
@@ -4013,7 +4049,7 @@
     </row>
     <row r="27" spans="1:35">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C27" s="11">
         <f>C18+C8+C9-C26</f>
@@ -4150,7 +4186,7 @@
     </row>
     <row r="28" spans="1:35">
       <c r="A28" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -4189,10 +4225,10 @@
     </row>
     <row r="29" spans="1:35">
       <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" t="s">
         <v>123</v>
-      </c>
-      <c r="B29" t="s">
-        <v>122</v>
       </c>
       <c r="C29" s="10">
         <f>C21+C22+C16+C24</f>
@@ -4329,10 +4365,10 @@
     </row>
     <row r="30" spans="1:35">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="10">
         <f>-C27</f>
@@ -4469,10 +4505,10 @@
     </row>
     <row r="31" spans="1:35">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C31" s="10">
         <v>4</v>
@@ -4537,46 +4573,10 @@
       <c r="W31" s="10">
         <v>17</v>
       </c>
-      <c r="X31" s="10">
-        <v>19</v>
-      </c>
-      <c r="Y31" s="10">
-        <v>21</v>
-      </c>
-      <c r="Z31" s="10">
-        <v>23</v>
-      </c>
-      <c r="AA31" s="10">
-        <v>25</v>
-      </c>
-      <c r="AB31" s="10">
-        <v>27</v>
-      </c>
-      <c r="AC31" s="10">
-        <v>29</v>
-      </c>
-      <c r="AD31" s="10">
-        <v>31</v>
-      </c>
-      <c r="AE31" s="10">
-        <v>33</v>
-      </c>
-      <c r="AF31" s="10">
-        <v>35</v>
-      </c>
-      <c r="AG31" s="10">
-        <v>37</v>
-      </c>
-      <c r="AH31" s="10">
-        <v>39</v>
-      </c>
-      <c r="AI31" s="10">
-        <v>41</v>
-      </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4597,40 +4597,40 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="10">
         <v>13</v>
@@ -4643,15 +4643,15 @@
         <v>121044</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C6" s="10">
         <v>14</v>
@@ -4664,15 +4664,15 @@
         <v>126420</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="10">
         <v>21</v>
@@ -4685,15 +4685,15 @@
         <v>167820</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="10">
         <v>32</v>
@@ -4706,15 +4706,15 @@
         <v>648864</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="10">
         <v>36</v>
@@ -4727,15 +4727,15 @@
         <v>290532</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="10">
         <v>40</v>
@@ -4748,15 +4748,15 @@
         <v>321060</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="10">
         <v>56</v>
@@ -4769,15 +4769,15 @@
         <v>385128</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" s="11">
         <f>SUM(C5:C11)</f>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="10">
         <v>1</v>
@@ -4809,15 +4809,15 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="10">
         <v>19</v>
@@ -4829,12 +4829,12 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E15" s="6">
         <f>E12+E13+E14</f>
@@ -4843,27 +4843,27 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="10">
         <v>2651</v>
@@ -4878,7 +4878,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="10">
         <v>6828</v>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="10">
         <v>10024</v>
@@ -4908,7 +4908,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" s="10">
         <v>12366</v>
@@ -4923,7 +4923,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="10">
         <v>16059</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C24" s="10">
         <v>19462</v>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" s="10">
         <v>23092</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26" s="10">
         <v>28610</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="10">
         <v>34539</v>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="10">
         <v>40585</v>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="10">
         <v>65867</v>
@@ -5028,7 +5028,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="10">
         <v>72656</v>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="10">
         <v>77134</v>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="10">
         <v>85778</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" s="10">
         <v>95824</v>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="10">
         <v>122664</v>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C35" s="10">
         <v>133652</v>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="10">
         <v>142497</v>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" s="10">
         <v>149831</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="10">
         <v>160971</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" s="10">
         <v>171739</v>
@@ -5178,7 +5178,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5198,73 +5198,73 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="10">
         <v>5</v>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="10">
         <v>6</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="10">
         <v>6</v>
@@ -5435,7 +5435,7 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="10">
         <v>7</v>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="10">
         <v>7</v>
@@ -5549,7 +5549,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B10" s="10">
         <v>7</v>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="10">
         <v>9</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="10">
         <v>10</v>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="10">
         <v>11</v>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" s="11">
         <f>SUM(B5:B13)</f>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -5818,40 +5818,40 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" s="10">
         <v>191000</v>
@@ -5863,13 +5863,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" s="10">
         <v>139000</v>
@@ -5881,13 +5881,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" s="10">
         <v>189000</v>
@@ -5899,13 +5899,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="10">
         <v>141000</v>
@@ -5917,13 +5917,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="10">
         <v>173500</v>
@@ -5935,13 +5935,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="10">
         <v>156500</v>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="10">
         <v>211000</v>
@@ -5971,13 +5971,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" s="10">
         <v>119000</v>
@@ -5989,13 +5989,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" s="10">
         <v>179000</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" s="10">
         <v>151000</v>
@@ -6025,13 +6025,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" s="10">
         <v>194500</v>
@@ -6043,13 +6043,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" s="10">
         <v>135500</v>
@@ -6061,13 +6061,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" s="10">
         <v>170500</v>
@@ -6079,13 +6079,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="10">
         <v>159500</v>
@@ -6097,13 +6097,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="10">
         <v>203000</v>
@@ -6115,13 +6115,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" s="10">
         <v>127000</v>
@@ -6133,13 +6133,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" s="10">
         <v>188000</v>
@@ -6151,13 +6151,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D22" s="10">
         <v>142000</v>
@@ -6169,13 +6169,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D23" s="10">
         <v>154500</v>
@@ -6187,13 +6187,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D24" s="10">
         <v>175500</v>
@@ -6205,13 +6205,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D25" s="10">
         <v>178500</v>
@@ -6223,13 +6223,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D26" s="10">
         <v>151500</v>
@@ -6241,13 +6241,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D27" s="10">
         <v>187000</v>
@@ -6259,13 +6259,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="10">
         <v>143000</v>
@@ -6277,25 +6277,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B29" s="6">
         <f>COUNTA(A5:A28)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B30" s="10">
-        <f>STAFF_NOW+B29</f>
-        <v>41</v>
-      </c>
-    </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6337,7 +6328,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6">
         <f>CASH_START</f>
@@ -6346,7 +6337,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>210</v>
@@ -6355,16 +6346,16 @@
         <v>211</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>212</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>213</v>
@@ -6378,7 +6369,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" s="10">
         <v>0</v>
@@ -6390,7 +6381,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="10">
         <v>1</v>
@@ -6424,7 +6415,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" s="10">
         <v>2</v>
@@ -6458,7 +6449,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="10">
         <v>3</v>
@@ -6492,7 +6483,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" s="10">
         <v>4</v>
@@ -6526,7 +6517,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" s="10">
         <v>5</v>
@@ -6560,7 +6551,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="10">
         <v>6</v>
@@ -6594,7 +6585,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" s="10">
         <v>7</v>
@@ -6628,7 +6619,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="10">
         <v>8</v>
@@ -6662,7 +6653,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="10">
         <v>9</v>
@@ -6696,7 +6687,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B18" s="10">
         <v>10</v>
@@ -6730,7 +6721,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B19" s="10">
         <v>11</v>
@@ -6764,7 +6755,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" s="10">
         <v>12</v>
@@ -8430,7 +8421,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -8460,13 +8451,13 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>266</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -8561,7 +8552,91 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="90.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" s="6">
+        <v>28000</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B6" s="6">
+        <v>9000</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="6">
+        <f>MARKET_CLINICS*MARKET_ACV_USD</f>
+        <v>252000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="10">
+        <f>ARR_Build!E12/ARR_Build!C12</f>
+        <v>9721.075471698114</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
